--- a/template_staff_export.xlsx
+++ b/template_staff_export.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCharm\programs\ARSA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCharm\programs\TSORORTTSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1CA940-15E7-4900-83A6-76130EBDBC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0512706-01D1-4D10-B438-AA8CEEB1124F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,24 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>ФИО</t>
-  </si>
-  <si>
-    <t>Наумов Арсений Германович</t>
-  </si>
-  <si>
-    <t>Соколова Ксения Дмитриевна</t>
-  </si>
-  <si>
-    <t>Алексеева Арина Даниэльевна</t>
-  </si>
-  <si>
-    <t>Кочеткова София Вячеславовна</t>
-  </si>
-  <si>
-    <t>Антипова Юлия Николаевна</t>
   </si>
 </sst>
 </file>
@@ -382,7 +367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -390,31 +375,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/template_staff_export.xlsx
+++ b/template_staff_export.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCharm\programs\TSORORTTSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0512706-01D1-4D10-B438-AA8CEEB1124F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689A12C0-FE65-4FFB-BDC7-309FDC51E109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>ФИО</t>
+  </si>
+  <si>
+    <t>Борисова Анна Ильинична</t>
+  </si>
+  <si>
+    <t>Назарова Александра Ярославовна</t>
+  </si>
+  <si>
+    <t>Николаев Иван Егорович</t>
+  </si>
+  <si>
+    <t>Румянцев Максим Алексеевич</t>
+  </si>
+  <si>
+    <t>Мельников Тимур Ильич</t>
   </si>
 </sst>
 </file>
@@ -367,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -375,6 +390,31 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/template_staff_export.xlsx
+++ b/template_staff_export.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCharm\programs\TSORORTTSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689A12C0-FE65-4FFB-BDC7-309FDC51E109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869CB681-034F-43DE-A115-02DF6B77FCD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,9 +30,6 @@
     <t>ФИО</t>
   </si>
   <si>
-    <t>Борисова Анна Ильинична</t>
-  </si>
-  <si>
     <t>Назарова Александра Ярославовна</t>
   </si>
   <si>
@@ -43,6 +40,9 @@
   </si>
   <si>
     <t>Мельников Тимур Ильич</t>
+  </si>
+  <si>
+    <t>Примеры: Борисова Анна Ильинична</t>
   </si>
 </sst>
 </file>
@@ -392,27 +392,27 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
